--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -589,6 +589,11 @@
           <t>https://ocen-piwo.pl/maryensztadt-summertime-papaja-mango-brzoskwinia-s1-n36566</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dawid: 1</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="54.75" customHeight="1">
       <c r="A3" s="1" t="n">
@@ -625,6 +630,11 @@
           <t>.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dawid: 3</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="1" t="n">
@@ -661,6 +671,11 @@
           <t>https://ocen-piwo.pl/trzech-kumpli-lager-wiedenski-s1-n25855</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dawid: 2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="1">
@@ -698,6 +713,11 @@
           <t>https://ocen-piwo.pl/magic-road-mochi-green-s1-n33867</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dawid: 3,5</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="1">
@@ -735,6 +755,11 @@
           <t>https://ocen-piwo.pl/gosciszewo-ogrod-mistrza-witbier-z-tymiankiem-cytrynowym-s1-n8343</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dawid: 1,25</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="1">
@@ -772,6 +797,11 @@
           <t>https://ocen-piwo.pl/stu-mostow-berry-up-s1-n36564</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dawid: 4,5</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="1">
@@ -809,6 +839,11 @@
           <t>https://browarpinta.pl/produkt/pinta-classics-mild/</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dawid: 2</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1">
@@ -846,6 +881,11 @@
           <t>https://ocen-piwo.pl/funky-fluid-gelato-purple-fluff-s1-n26711</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dawid: 4</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="1">
@@ -883,6 +923,11 @@
           <t>https://browarpinta.pl/produkt/pinta-summer-beer-supply-polish-cold-ipa/</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dawid: 1,25</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="1">
@@ -920,6 +965,11 @@
           <t>https://ocen-piwo.pl/nepomucen-smoothie-bowl-sweet-morning-s1-n33621</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dawid: 2,5</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="1">
@@ -957,6 +1007,11 @@
           <t>https://ocen-piwo.pl/amber-po-godzinach-graff-apple-wheat-s1-n5590</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dawid: 3</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1">
@@ -994,6 +1049,11 @@
           <t>https://www.lidl.pl/p/za-miastem-wolny-wieczor/p10035546</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dawid: 2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="1">
@@ -1031,6 +1091,11 @@
           <t>https://ocen-piwo.pl/bojan-bananowe-s1-n29230</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dawid: 2</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="1">
@@ -1068,6 +1133,11 @@
           <t>https://browarzakladowy.pl/sokowirowka-kwasne-ale-z-malinami-i-jagodami/</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dawid: 1,5</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="1">
@@ -1105,6 +1175,11 @@
           <t>https://ocen-piwo.pl/funky-fluid-farm-to-glass-26-citra-s1-n36167</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dawid: 2,5</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="1">
@@ -1142,6 +1217,11 @@
           <t>https://ocen-piwo.pl/zakladowy-hiszpanskie-wakacje-s1-n34316</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dawid: 2,5</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="1">
@@ -1179,6 +1259,11 @@
           <t>https://browarzakladowy.pl/wyjac-grilla-to-jest-chwila-new-zealand-west-coast-ipa/</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dawid: 2</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="1" t="n">
@@ -1213,6 +1298,11 @@
       <c r="H19" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/litovel-cerny-citron-s1-n3209</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dawid: 4</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Dawid: 3</t>
+          <t>Dawid: 3; Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dawid: 3,5</t>
+          <t>Dawid: 3,5; Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Dawid: 1,25</t>
+          <t>Dawid: 1,25; Jastrząb: 2,75</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.5</v>
+        <v>4.12</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dawid: 4,5</t>
+          <t>Dawid: 4,5; Jastrząb: 3,75</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dawid: 4</t>
+          <t>Dawid: 4; Jastrząb: 3,5</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dawid: 3</t>
+          <t>Dawid: 3; Jastrząb: 1</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 3,25</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 3,25</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dawid: 1,5</t>
+          <t>Dawid: 1,5; Jastrząb: 1,25</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Dawid: 2,5</t>
+          <t>Dawid: 2,5; Jastrząb: 3</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Dawid: 2,5</t>
+          <t>Dawid: 2,5; Jastrząb: 3,25</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dawid: 4</t>
+          <t>Dawid: 4; Jastrząb: 4</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1356,17 @@
           <t>Sour</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>1.75</v>
+      </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/bojan-kwasna-marakuja-s1-n27291</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -1412,9 +1420,17 @@
           <t>HOP Selection NEIPA</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/funky-fluid-farm-to-glass-26-mosaic-s1-n36096</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Jastrząb: 3</t>
         </is>
       </c>
     </row>
@@ -1468,9 +1484,17 @@
           <t>HOP Selection NEIPA</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/funky-fluid-farm-to-glass-26-simcoe-s1-n36112</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Jastrząb: 1,5</t>
         </is>
       </c>
     </row>
@@ -1492,16 +1516,64 @@
           <t>Stout</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/guinness-draught-s1-n253</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MlodyD: Komentarz zbędny (20.07.2026) | zaskurio de lima: Bardzo duzy plus jest taki, ze trzeba zamowic tak duzo az uda sie split the g (20.07.2026)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Jastrząb: 5; MlodyD: 5; zaskurio de lima: 5</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="1">
-        <f>IF(ISBLANK(B27),"",ROW(B27)-1)</f>
-        <v/>
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Grupa Żywiec</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Królewskie</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Jasne</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>dodane przez: Koneser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Koneser: Doskonała jakość i smak, szczególnie ciepły w puszce (20.07.2026)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Koneser: 5</t>
+        </is>
       </c>
     </row>
     <row r="28">

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dawid: 2,5</t>
+          <t>Dawid: 2,5; Jastrząb: 2</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2.38</v>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dawid: 1</t>
+          <t>Dawid: 1; Jastrząb: 3,75</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 1,5</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dawid: 1,25</t>
+          <t>Dawid: 1,25; Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -1300,6 +1300,11 @@
           <t>https://ocen-piwo.pl/litovel-cerny-citron-s1-n3209</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jastrząb: No przepyszny jest, może i dla kobiet w ciąży ale orzeźwiający i daje Liptonem (22.07.2026)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Dawid: 4; Jastrząb: 4</t>
@@ -1328,9 +1333,17 @@
           <t>Modern West Coast IPA</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/pinta-summer-beer-supply-modern-west-coast-ipa-s1-n36830</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Jastrząb: 1,5</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1370,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
@@ -1366,7 +1379,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Jastrząb: 1,75</t>
+          <t>Jastrząb: 2</t>
         </is>
       </c>
     </row>
@@ -1392,9 +1405,17 @@
           <t>Northern IPA</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>2.25</v>
+      </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/inne-beczki-hopgang-aurora-s1-n35274</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Jastrząb: 2,25</t>
         </is>
       </c>
     </row>
@@ -1456,9 +1477,17 @@
           <t>Session Hazy IPA</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>1.75</v>
+      </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
           <t>https://ocen-piwo.pl/pinta-summer-beer-supply-session-hazy-ipa-s1-n36840</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1587,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1572,7 +1601,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Koneser: 5</t>
+          <t>Jastrząb: 1; Koneser: 5</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.38</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dawid: 1; Jastrząb: 3,75</t>
+          <t>Dawid: 1</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dawid: 2; Jastrząb: 2</t>
+          <t>Dawid: 2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dawid: 2; Jastrząb: 1,5</t>
+          <t>Dawid: 2</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dawid: 1,25; Jastrząb: 1,75</t>
+          <t>Dawid: 1,25</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dawid: 2,5; Jastrząb: 2</t>
+          <t>Dawid: 2,5</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Jastrząb: 2</t>
+          <t>Jastrząb: 1,75</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Jastrząb: 1; Koneser: 5</t>
+          <t>Koneser: 5</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2.12</v>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dawid: 1</t>
+          <t>Dawid: 1; Jastrząb: 3,25</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 2,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Dawid: 2</t>
+          <t>Dawid: 2; Jastrząb: 1</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dawid: 1,25</t>
+          <t>Dawid: 1,25; Jastrząb: 1,5</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dawid: 2,5</t>
+          <t>Dawid: 2,5; Jastrząb: 3</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Koneser: 5</t>
+          <t>Jastrząb: 0,5; Koneser: 5</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Dawid: 1,25; Jastrząb: 1,5</t>
+          <t>Dawid: 1,25; Jastrzab: 3,25; Jastrząb: 1,5</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -1606,9 +1606,44 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1">
-        <f>IF(ISBLANK(B28),"",ROW(B28)-1)</f>
-        <v/>
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Romper strong</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Premium Romper Strong</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Podlak</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>dodane przez: Medzz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Medzz: mocne i charakterne (10.08.2026)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Medzz: 5</t>
+        </is>
       </c>
     </row>
     <row r="29">

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -1647,9 +1647,39 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1">
-        <f>IF(ISBLANK(B29),"",ROW(B29)-1)</f>
-        <v/>
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Surf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Przeniczne</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Przeniczne</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>dodane przez: Jastrząb</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Jastrząb: 4</t>
+        </is>
       </c>
     </row>
     <row r="30">

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Dawid: 1,5; Jastrząb: 1,25</t>
+          <t>Cwel: 2,5; Dawid: 1,5; Jastrząb: 1,25</t>
         </is>
       </c>
     </row>

--- a/Piwa.xlsx
+++ b/Piwa.xlsx
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dawid: 4; Jastrząb: 4</t>
+          <t>Dawid: 4; Jastrząb: 4; Miras: 4,25</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Jastrząb: 0,5; Koneser: 5</t>
+          <t>Jastrząb: 0,5; Koneser: 5; Miras: 3</t>
         </is>
       </c>
     </row>
